--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97298</v>
+        <v>97314</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>113314615</v>
       </c>
       <c r="B13" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,6 +2233,135 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122575166</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lomtjärnsheden, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557679</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6626388</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>+ lockläte</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2238,7 +2238,7 @@
         <v>122575166</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -2238,7 +2238,7 @@
         <v>122575166</v>
       </c>
       <c r="B14" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 13994-2023 artfynd.xlsx
+++ b/artfynd/A 13994-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,69 +2102,65 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113314615</v>
+        <v>122575166</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomtjärnsheden (knärot), Vstm</t>
+          <t>Lomtjärnsheden, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557645</v>
+        <v>557679</v>
       </c>
       <c r="R13" t="n">
-        <v>6626655</v>
+        <v>6626388</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2186,24 +2182,29 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>U-Sur-0527</t>
-        </is>
-      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>438/250 (5), 1 m2, 436/254 (5), 2 m2, spridda bladrosetter</t>
+          <t>+ lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,155 +2213,21 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>122575166</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Lomtjärnsheden, Ramnäs sn, Vstm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>557679</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6626388</v>
-      </c>
-      <c r="S14" t="n">
-        <v>50</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-02-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>+ lockläte</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
           <t>Sören Larsson</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
